--- a/access_control_forms/016_preventive_maintenance_access_control_form--access_control_forms.xlsx
+++ b/access_control_forms/016_preventive_maintenance_access_control_form--access_control_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -757,8 +757,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -786,12 +786,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'maintenance_worker'}</t>
+          <t>maintenance_worker</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Maintenance Worker'}</t>
+          <t>Maintenance Worker</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'maintenance_manager'}</t>
+          <t>maintenance_manager</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Maintenance Manager'}</t>
+          <t>Maintenance Manager</t>
         </is>
       </c>
     </row>
@@ -820,12 +820,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'maintenance_supervisor'}</t>
+          <t>maintenance_supervisor</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Maintenance Supervisor'}</t>
+          <t>Maintenance Supervisor</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'scheduled'}</t>
+          <t>scheduled</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Scheduled'}</t>
+          <t>Scheduled</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'unscheduled'}</t>
+          <t>unscheduled</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Unscheduled'}</t>
+          <t>Unscheduled</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'emergency'}</t>
+          <t>emergency</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Emergency'}</t>
+          <t>Emergency</t>
         </is>
       </c>
     </row>
@@ -939,12 +939,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'supervisor'}</t>
+          <t>supervisor</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Supervisor'}</t>
+          <t>Supervisor</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Manager'}</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -973,12 +973,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'employee'}</t>
+          <t>employee</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Employee'}</t>
+          <t>Employee</t>
         </is>
       </c>
     </row>
